--- a/Hyderabad-March-2026.xlsx
+++ b/Hyderabad-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="70">
   <si>
     <t>Sr. No</t>
   </si>
@@ -148,13 +148,13 @@
     <t>MH43BP4027</t>
   </si>
   <si>
-    <t>TS09UE 3183</t>
-  </si>
-  <si>
-    <t>TS09UE 3184</t>
-  </si>
-  <si>
-    <t>TS09UE 3198</t>
+    <t>TS09UE3183</t>
+  </si>
+  <si>
+    <t>TS09UE3184</t>
+  </si>
+  <si>
+    <t>TS09UE3198</t>
   </si>
   <si>
     <t>TS09UE3947</t>
@@ -175,25 +175,25 @@
     <t>JAGUAR</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Etios</t>
-  </si>
-  <si>
-    <t>Bolero</t>
-  </si>
-  <si>
-    <t>Safari</t>
-  </si>
-  <si>
-    <t>BYD</t>
-  </si>
-  <si>
-    <t>Dzire</t>
+    <t>ETIOS</t>
+  </si>
+  <si>
+    <t>BOLERO</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>BYD E6</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>29/09/2018</t>
@@ -221,9 +221,6 @@
   </si>
   <si>
     <t>17/07/2019</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>14/03/2024</t>
@@ -1970,8 +1967,8 @@
       <c r="F18" t="s">
         <v>56</v>
       </c>
-      <c r="G18" t="s">
-        <v>69</v>
+      <c r="G18" s="2">
+        <v>45352</v>
       </c>
       <c r="H18">
         <v>59194</v>
@@ -2050,8 +2047,8 @@
       <c r="F19" t="s">
         <v>56</v>
       </c>
-      <c r="G19" t="s">
-        <v>69</v>
+      <c r="G19" s="2">
+        <v>45352</v>
       </c>
       <c r="H19">
         <v>135022</v>
@@ -2130,8 +2127,8 @@
       <c r="F20" t="s">
         <v>56</v>
       </c>
-      <c r="G20" t="s">
-        <v>69</v>
+      <c r="G20" s="2">
+        <v>45352</v>
       </c>
       <c r="H20">
         <v>140437</v>
@@ -2371,7 +2368,7 @@
         <v>58</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H23">
         <v>77545</v>
